--- a/public/aiviral_data.xlsx
+++ b/public/aiviral_data.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="123">
   <si>
     <t xml:space="preserve"> Company/Brand Name</t>
   </si>
@@ -296,6 +296,21 @@
   </si>
   <si>
     <t>https://res.cloudinary.com/dt4xjvs3q/image/upload/v1769421293/Realistic_skincare_product_2k_202601261520_llrrww.jpg</t>
+  </si>
+  <si>
+    <t>Indimums</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dt4xjvs3q/image/upload/v1769437313/indimums_baby_body_wash_200ml_kqttls.webp</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dt4xjvs3q/video/upload/v1769433007/8second_cinematic_product_1080p_202601261818_online-video-cutter.com_yyolry.mp4</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dt4xjvs3q/image/upload/v1769433000/Natural_lifestyle_product_2k_202601261806_pvivju.jpg</t>
+  </si>
+  <si>
+    <t>https://res.cloudinary.com/dt4xjvs3q/image/upload/v1769433000/Ultrarealistic_product_photoshoot_2k_2026012_o2ph6i.jpg</t>
   </si>
   <si>
     <t>Name</t>
@@ -4252,6 +4267,29 @@
         <v>71</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>76</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="B2"/>
@@ -4266,8 +4304,14 @@
     <hyperlink r:id="rId10" ref="E3"/>
     <hyperlink r:id="rId11" ref="F3"/>
     <hyperlink r:id="rId12" ref="G3"/>
+    <hyperlink r:id="rId13" ref="B4"/>
+    <hyperlink r:id="rId14" ref="C4"/>
+    <hyperlink r:id="rId15" ref="D4"/>
+    <hyperlink r:id="rId16" ref="E4"/>
+    <hyperlink r:id="rId17" ref="F4"/>
+    <hyperlink r:id="rId18" ref="G4"/>
   </hyperlinks>
-  <drawing r:id="rId13"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -4284,16 +4328,16 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
@@ -4320,222 +4364,222 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
